--- a/Proyecto Interno/interno/output/lista alimentos/lista_total_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/lista_total_alimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="413">
   <si>
     <t xml:space="preserve">sku_code</t>
   </si>
@@ -443,6 +443,18 @@
     <t xml:space="preserve">Cebolla junca</t>
   </si>
   <si>
+    <t xml:space="preserve">1601991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cebolla puerro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">463597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cebollín chino</t>
+  </si>
+  <si>
     <t xml:space="preserve">584368</t>
   </si>
   <si>
@@ -467,6 +479,12 @@
     <t xml:space="preserve">Coco</t>
   </si>
   <si>
+    <t xml:space="preserve">909686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coles</t>
+  </si>
+  <si>
     <t xml:space="preserve">923325</t>
   </si>
   <si>
@@ -506,12 +524,21 @@
     <t xml:space="preserve">Durazno importado</t>
   </si>
   <si>
+    <t xml:space="preserve">3181314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durazno nacional</t>
+  </si>
+  <si>
     <t xml:space="preserve">909698</t>
   </si>
   <si>
     <t xml:space="preserve">Espinaca</t>
   </si>
   <si>
+    <t xml:space="preserve">909704</t>
+  </si>
+  <si>
     <t xml:space="preserve">1720</t>
   </si>
   <si>
@@ -650,6 +677,12 @@
     <t xml:space="preserve">Huevo blanco AA</t>
   </si>
   <si>
+    <t xml:space="preserve">445563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huevo blanco extra</t>
+  </si>
+  <si>
     <t xml:space="preserve">1032680</t>
   </si>
   <si>
@@ -695,6 +728,12 @@
     <t xml:space="preserve">Kiwi</t>
   </si>
   <si>
+    <t xml:space="preserve">973260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langostino 16-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">1783394</t>
   </si>
   <si>
@@ -719,6 +758,12 @@
     <t xml:space="preserve">Limón Tahití</t>
   </si>
   <si>
+    <t xml:space="preserve">1599636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limón común</t>
+  </si>
+  <si>
     <t xml:space="preserve">3649838</t>
   </si>
   <si>
@@ -752,6 +797,12 @@
     <t xml:space="preserve">Mango Tommy</t>
   </si>
   <si>
+    <t xml:space="preserve">395124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mango común</t>
+  </si>
+  <si>
     <t xml:space="preserve">3099853</t>
   </si>
   <si>
@@ -869,6 +920,9 @@
     <t xml:space="preserve">Panela redonda morena</t>
   </si>
   <si>
+    <t xml:space="preserve">107688</t>
+  </si>
+  <si>
     <t xml:space="preserve">1421</t>
   </si>
   <si>
@@ -881,6 +935,9 @@
     <t xml:space="preserve">Papa criolla limpia</t>
   </si>
   <si>
+    <t xml:space="preserve">1784</t>
+  </si>
+  <si>
     <t xml:space="preserve">1790</t>
   </si>
   <si>
@@ -926,6 +983,12 @@
     <t xml:space="preserve">Patilla baby</t>
   </si>
   <si>
+    <t xml:space="preserve">1582160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pechuga de pollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">1601909</t>
   </si>
   <si>
@@ -1019,6 +1082,9 @@
     <t xml:space="preserve">Queso campesino</t>
   </si>
   <si>
+    <t xml:space="preserve">3267163</t>
+  </si>
+  <si>
     <t xml:space="preserve">577601</t>
   </si>
   <si>
@@ -1055,6 +1121,12 @@
     <t xml:space="preserve">Repollo morado</t>
   </si>
   <si>
+    <t xml:space="preserve">141467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rábano rojo</t>
+  </si>
+  <si>
     <t xml:space="preserve">21070</t>
   </si>
   <si>
@@ -1094,6 +1166,12 @@
     <t xml:space="preserve">Sardinas en lata</t>
   </si>
   <si>
+    <t xml:space="preserve">861947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra entera congelada</t>
+  </si>
+  <si>
     <t xml:space="preserve">3320362</t>
   </si>
   <si>
@@ -1130,6 +1208,12 @@
     <t xml:space="preserve">Tomate larga vida</t>
   </si>
   <si>
+    <t xml:space="preserve">723282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trucha en corte mariposa</t>
+  </si>
+  <si>
     <t xml:space="preserve">1851</t>
   </si>
   <si>
@@ -1142,6 +1226,12 @@
     <t xml:space="preserve">Ulluco</t>
   </si>
   <si>
+    <t xml:space="preserve">1823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uva Isabela</t>
+  </si>
+  <si>
     <t xml:space="preserve">1101</t>
   </si>
   <si>
@@ -1158,6 +1248,9 @@
   </si>
   <si>
     <t xml:space="preserve">Zanahoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3641889</t>
   </si>
 </sst>
 </file>
@@ -2187,44 +2280,44 @@
         <v>155</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B90" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B91" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B93" t="s">
         <v>163</v>
@@ -2232,10 +2325,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B94" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95">
@@ -2251,31 +2344,31 @@
         <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" t="s">
         <v>173</v>
-      </c>
-      <c r="B99" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="100">
@@ -2307,31 +2400,31 @@
         <v>180</v>
       </c>
       <c r="B103" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B104" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>186</v>
+      </c>
+      <c r="B106" t="s">
         <v>185</v>
-      </c>
-      <c r="B106" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="107">
@@ -2355,39 +2448,39 @@
         <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" t="s">
         <v>197</v>
-      </c>
-      <c r="B113" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="114">
@@ -2395,23 +2488,23 @@
         <v>199</v>
       </c>
       <c r="B114" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>200</v>
+      </c>
+      <c r="B115" t="s">
         <v>201</v>
-      </c>
-      <c r="B115" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116" t="s">
         <v>203</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117">
@@ -2427,28 +2520,28 @@
         <v>206</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B119" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B121" t="s">
         <v>211</v>
@@ -2456,18 +2549,18 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>215</v>
+      </c>
+      <c r="B123" t="s">
         <v>214</v>
-      </c>
-      <c r="B123" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="124">
@@ -2475,7 +2568,7 @@
         <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="125">
@@ -2483,60 +2576,60 @@
         <v>217</v>
       </c>
       <c r="B125" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B126" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B130" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B131" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B132" t="s">
         <v>226</v>
@@ -2544,23 +2637,23 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B134" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B135" t="s">
         <v>232</v>
@@ -2568,10 +2661,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137">
@@ -2579,15 +2672,15 @@
         <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="139">
@@ -2651,28 +2744,28 @@
         <v>252</v>
       </c>
       <c r="B146" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>253</v>
+      </c>
+      <c r="B147" t="s">
         <v>254</v>
-      </c>
-      <c r="B147" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>255</v>
+      </c>
+      <c r="B148" t="s">
         <v>256</v>
-      </c>
-      <c r="B148" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B149" t="s">
         <v>258</v>
@@ -2715,36 +2808,36 @@
         <v>267</v>
       </c>
       <c r="B154" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B158" t="s">
         <v>275</v>
@@ -2771,23 +2864,23 @@
         <v>280</v>
       </c>
       <c r="B161" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B162" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
+        <v>284</v>
+      </c>
+      <c r="B163" t="s">
         <v>283</v>
-      </c>
-      <c r="B163" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="164">
@@ -2811,39 +2904,39 @@
         <v>289</v>
       </c>
       <c r="B166" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B167" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B168" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B169" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
+        <v>297</v>
+      </c>
+      <c r="B170" t="s">
         <v>296</v>
-      </c>
-      <c r="B170" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="171">
@@ -2867,231 +2960,231 @@
         <v>302</v>
       </c>
       <c r="B173" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>303</v>
+      </c>
+      <c r="B174" t="s">
         <v>304</v>
-      </c>
-      <c r="B174" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
+        <v>305</v>
+      </c>
+      <c r="B175" t="s">
         <v>306</v>
-      </c>
-      <c r="B175" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B176" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B177" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B178" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B179" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B180" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B181" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B182" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B183" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B184" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B185" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B186" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B187" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B188" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B189" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B190" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B191" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B192" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B193" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B194" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B195" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B196" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B197" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B198" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>350</v>
+      </c>
+      <c r="B199" t="s">
         <v>351</v>
-      </c>
-      <c r="B199" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>352</v>
+      </c>
+      <c r="B200" t="s">
         <v>353</v>
-      </c>
-      <c r="B200" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
+        <v>354</v>
+      </c>
+      <c r="B201" t="s">
         <v>355</v>
-      </c>
-      <c r="B201" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="202">
@@ -3099,7 +3192,7 @@
         <v>356</v>
       </c>
       <c r="B202" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="203">
@@ -3107,71 +3200,71 @@
         <v>357</v>
       </c>
       <c r="B203" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B204" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B205" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B206" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B207" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B208" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B209" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B210" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
+        <v>373</v>
+      </c>
+      <c r="B211" t="s">
         <v>372</v>
-      </c>
-      <c r="B211" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="212">
@@ -3179,31 +3272,175 @@
         <v>374</v>
       </c>
       <c r="B212" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
+        <v>375</v>
+      </c>
+      <c r="B213" t="s">
         <v>376</v>
-      </c>
-      <c r="B213" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
+        <v>377</v>
+      </c>
+      <c r="B214" t="s">
         <v>378</v>
-      </c>
-      <c r="B214" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
+        <v>379</v>
+      </c>
+      <c r="B215" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
         <v>380</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B216" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
         <v>381</v>
+      </c>
+      <c r="B217" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>382</v>
+      </c>
+      <c r="B218" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>384</v>
+      </c>
+      <c r="B219" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>386</v>
+      </c>
+      <c r="B220" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>388</v>
+      </c>
+      <c r="B221" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>390</v>
+      </c>
+      <c r="B222" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>392</v>
+      </c>
+      <c r="B223" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>394</v>
+      </c>
+      <c r="B224" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>396</v>
+      </c>
+      <c r="B225" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>398</v>
+      </c>
+      <c r="B226" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>400</v>
+      </c>
+      <c r="B227" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>402</v>
+      </c>
+      <c r="B228" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>404</v>
+      </c>
+      <c r="B229" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>406</v>
+      </c>
+      <c r="B230" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>408</v>
+      </c>
+      <c r="B231" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>410</v>
+      </c>
+      <c r="B232" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>412</v>
+      </c>
+      <c r="B233" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
